--- a/Config/Datas/Tables/z_战斗表现_CombatPresentationConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗表现_CombatPresentationConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombatPresentationConfig" sheetId="1" r:id="R5ae3b214490d4601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombatPresentationConfig" sheetId="1" r:id="R95d69ea5718c4229"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,33 +604,23 @@
       <x:c r="T1" s="11" t="str">
         <x:v>helpText</x:v>
       </x:c>
-      <x:c r="U1" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">panelWidthMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V1" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">panelHeightMilli</x:t>
-        </x:is>
+      <x:c r="U1" s="11" t="str">
+        <x:v>panelWidthPixels</x:v>
+      </x:c>
+      <x:c r="V1" s="11" t="str">
+        <x:v>panelHeightPixels</x:v>
       </x:c>
       <x:c r="W1" s="11" t="str">
         <x:v>fontSize</x:v>
       </x:c>
-      <x:c r="X1" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cameraDepthMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y1" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cameraNearMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z1" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cameraFarMilli</x:t>
-        </x:is>
+      <x:c r="X1" s="11" t="str">
+        <x:v>cameraDepthPixels</x:v>
+      </x:c>
+      <x:c r="Y1" s="11" t="str">
+        <x:v>cameraNearPixels</x:v>
+      </x:c>
+      <x:c r="Z1" s="11" t="str">
+        <x:v>cameraFarPixels</x:v>
       </x:c>
       <x:c r="AA1" s="11" t="inlineStr">
         <x:is>
@@ -699,10 +689,10 @@
         <x:v>feedbackRenderQueue</x:v>
       </x:c>
       <x:c r="AS1" s="38" t="str">
-        <x:v>healthBarWidthPixelsMilli</x:v>
+        <x:v>healthBarWidthPixels</x:v>
       </x:c>
       <x:c r="AT1" s="38" t="str">
-        <x:v>healthBarHeightPixelsMilli</x:v>
+        <x:v>healthBarHeightPixels</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
@@ -766,33 +756,23 @@
       <x:c r="T2" s="12" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="U2" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V2" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
+      <x:c r="U2" s="12" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="V2" s="12" t="str">
+        <x:v>float</x:v>
       </x:c>
       <x:c r="W2" s="12" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="X2" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y2" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z2" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
+      <x:c r="X2" s="12" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Y2" s="12" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Z2" s="12" t="str">
+        <x:v>float</x:v>
       </x:c>
       <x:c r="AA2" s="12" t="inlineStr">
         <x:is>
@@ -861,10 +841,10 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="AS2" s="39" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="AT2" s="39" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -978,33 +958,23 @@
       <x:c r="T4" s="8" t="str">
         <x:v>操作说明</x:v>
       </x:c>
-      <x:c r="U4" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">调试面板像素宽；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V4" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">调试面板像素高；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="U4" s="8" t="str">
+        <x:v>调试面板宽度，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="V4" s="8" t="str">
+        <x:v>调试面板高度，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="W4" s="8" t="str">
         <x:v>调试文字字号</x:v>
       </x:c>
-      <x:c r="X4" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">相机距XY平面距离；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Y4" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">相机近裁面；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Z4" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">相机远裁面；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="X4" s="8" t="str">
+        <x:v>相机距XY平面距离，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="Y4" s="8" t="str">
+        <x:v>相机近裁面，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="Z4" s="8" t="str">
+        <x:v>相机远裁面，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="AA4" s="8" t="inlineStr">
         <x:is>
@@ -1073,10 +1043,10 @@
         <x:v>血条和伤害数字的透明渲染队列；必须高于技能。</x:v>
       </x:c>
       <x:c r="AS4" s="24" t="str">
-        <x:v>战斗血条最终显示宽度；逻辑像素×1000，由 CombatHealthBar Prefab 导出。</x:v>
+        <x:v>战斗血条最终显示宽度；由 CombatHealthBar Prefab 导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="AT4" s="24" t="str">
-        <x:v>战斗血条最终显示高度；逻辑像素×1000，由 CombatHealthBar Prefab 导出。</x:v>
+        <x:v>战斗血条最终显示高度；由 CombatHealthBar Prefab 导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
@@ -1138,23 +1108,23 @@
       <x:c r="T5" s="8" t="str">
         <x:v>WASD / 方向键移动；Esc 暂停；R 重开</x:v>
       </x:c>
-      <x:c r="U5" s="8">
-        <x:v>560000</x:v>
-      </x:c>
-      <x:c r="V5" s="8">
-        <x:v>150000</x:v>
+      <x:c r="U5" s="8" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="V5" s="8" t="n">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="W5" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="X5" s="8">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="Y5" s="8">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="Z5" s="8">
-        <x:v>50000</x:v>
+      <x:c r="X5" s="8" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="Y5" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z5" s="8" t="n">
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="AA5" s="8">
         <x:v>25</x:v>
@@ -1210,11 +1180,11 @@
       <x:c r="AR5" s="24" t="n">
         <x:v>3020</x:v>
       </x:c>
-      <x:c r="AS5" s="24">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="AT5" s="24">
-        <x:v>7000</x:v>
+      <x:c r="AS5" s="24" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AT5" s="24" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
